--- a/results/trace_selected25_full_temp06_seed44_answer_3b7b_results.xlsx
+++ b/results/trace_selected25_full_temp06_seed44_answer_3b7b_results.xlsx
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>20.55837563451777</v>
+        <v>34.0102</v>
       </c>
       <c r="F17" t="n">
         <v>788</v>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>20.43147208121827</v>
+        <v>39.9746</v>
       </c>
       <c r="I17" t="n">
         <v>788</v>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>22.84263959390863</v>
+        <v>44.1624</v>
       </c>
       <c r="L17" t="n">
         <v>788</v>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>25</v>
+        <v>47.335</v>
       </c>
       <c r="O17" t="n">
         <v>788</v>
@@ -2179,22 +2179,22 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>35.60992983965809</v>
+        <v>36.14800281427738</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>38.9657175095605</v>
+        <v>39.74744262631177</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>43.354847563305</v>
+        <v>44.20763797954865</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>47.50070710907003</v>
+        <v>48.39410710907003</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -2213,22 +2213,22 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>34.28641800645727</v>
+        <v>34.84691068835235</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>37.80168425065592</v>
+        <v>38.61598124727183</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
-        <v>42.11491589731065</v>
+        <v>43.00323924756444</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>46.25663279836304</v>
+        <v>47.18725779836304</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>

--- a/results/trace_selected25_full_temp06_seed44_answer_3b7b_results.xlsx
+++ b/results/trace_selected25_full_temp06_seed44_answer_3b7b_results.xlsx
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67.37421383647799</v>
+        <v>71.0691823899371</v>
       </c>
       <c r="F4" t="n">
         <v>1272</v>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>66.90251572327044</v>
+        <v>70.36163522012579</v>
       </c>
       <c r="I4" t="n">
         <v>1272</v>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>73.11320754716981</v>
+        <v>72.72012578616352</v>
       </c>
       <c r="L4" t="n">
         <v>1272</v>
@@ -2382,13 +2382,13 @@
         <v>1272</v>
       </c>
       <c r="F4" t="n">
-        <v>67.37421383647799</v>
+        <v>71.0691823899371</v>
       </c>
       <c r="G4" t="n">
-        <v>66.90251572327044</v>
+        <v>70.36163522012579</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4716981132075517</v>
+        <v>-0.7075471698113063</v>
       </c>
     </row>
     <row r="5">
@@ -3336,13 +3336,13 @@
         <v>1272</v>
       </c>
       <c r="F4" t="n">
-        <v>73.11320754716981</v>
+        <v>72.72012578616352</v>
       </c>
       <c r="G4" t="n">
         <v>77.35849056603774</v>
       </c>
       <c r="H4" t="n">
-        <v>4.245283018867937</v>
+        <v>4.638364779874223</v>
       </c>
     </row>
     <row r="5">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>67.37421383647799</v>
+        <v>71.0691823899371</v>
       </c>
       <c r="I10" t="n">
         <v>1272</v>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>66.90251572327044</v>
+        <v>70.36163522012579</v>
       </c>
       <c r="I11" t="n">
         <v>1272</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>73.11320754716981</v>
+        <v>72.72012578616352</v>
       </c>
       <c r="I12" t="n">
         <v>1272</v>

--- a/results/trace_selected25_full_temp06_seed44_answer_3b7b_results.xlsx
+++ b/results/trace_selected25_full_temp06_seed44_answer_3b7b_results.xlsx
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17.89383561643836</v>
+        <v>19.17808219178082</v>
       </c>
       <c r="F10" t="n">
         <v>1168</v>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>19.00684931506849</v>
+        <v>21.06164383561644</v>
       </c>
       <c r="I10" t="n">
         <v>1168</v>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>18.57876712328767</v>
+        <v>20.80479452054794</v>
       </c>
       <c r="L10" t="n">
         <v>1168</v>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>21.83219178082192</v>
+        <v>23.63013698630137</v>
       </c>
       <c r="O10" t="n">
         <v>1168</v>
@@ -2586,13 +2586,13 @@
         <v>1168</v>
       </c>
       <c r="F10" t="n">
-        <v>17.89383561643836</v>
+        <v>19.17808219178082</v>
       </c>
       <c r="G10" t="n">
-        <v>19.00684931506849</v>
+        <v>21.06164383561644</v>
       </c>
       <c r="H10" t="n">
-        <v>1.113013698630137</v>
+        <v>1.88356164383562</v>
       </c>
     </row>
     <row r="11">
@@ -3540,13 +3540,13 @@
         <v>1168</v>
       </c>
       <c r="F10" t="n">
-        <v>18.57876712328767</v>
+        <v>20.80479452054794</v>
       </c>
       <c r="G10" t="n">
-        <v>21.83219178082192</v>
+        <v>23.63013698630137</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25342465753425</v>
+        <v>2.825342465753426</v>
       </c>
     </row>
     <row r="11">
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>17.89383561643836</v>
+        <v>19.17808219178082</v>
       </c>
       <c r="I34" t="n">
         <v>1168</v>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>19.00684931506849</v>
+        <v>21.06164383561644</v>
       </c>
       <c r="I35" t="n">
         <v>1168</v>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>18.57876712328767</v>
+        <v>20.80479452054794</v>
       </c>
       <c r="I36" t="n">
         <v>1168</v>
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>21.83219178082192</v>
+        <v>23.63013698630137</v>
       </c>
       <c r="I37" t="n">
         <v>1168</v>

--- a/results/trace_selected25_full_temp06_seed44_answer_3b7b_results.xlsx
+++ b/results/trace_selected25_full_temp06_seed44_answer_3b7b_results.xlsx
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>34.0102</v>
+        <v>34.0101522843</v>
       </c>
       <c r="F17" t="n">
         <v>788</v>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>39.9746</v>
+        <v>39.9746192893</v>
       </c>
       <c r="I17" t="n">
         <v>788</v>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>44.1624</v>
+        <v>44.1624365482</v>
       </c>
       <c r="L17" t="n">
         <v>788</v>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>47.335</v>
+        <v>47.3350253807</v>
       </c>
       <c r="O17" t="n">
         <v>788</v>
@@ -2824,13 +2824,13 @@
         <v>788</v>
       </c>
       <c r="F17" t="n">
-        <v>20.55837563451777</v>
+        <v>34.0101522843</v>
       </c>
       <c r="G17" t="n">
-        <v>20.43147208121827</v>
+        <v>39.9746192893</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.126903553299492</v>
+        <v>5.964467005000003</v>
       </c>
     </row>
     <row r="18">
@@ -3778,13 +3778,13 @@
         <v>788</v>
       </c>
       <c r="F17" t="n">
-        <v>22.84263959390863</v>
+        <v>44.1624365482</v>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>47.3350253807</v>
       </c>
       <c r="H17" t="n">
-        <v>2.157360406091371</v>
+        <v>3.172588832500004</v>
       </c>
     </row>
     <row r="18">
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>20.55837563451777</v>
+        <v>34.0101522843</v>
       </c>
       <c r="I62" t="n">
         <v>788</v>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>20.43147208121827</v>
+        <v>39.9746192893</v>
       </c>
       <c r="I63" t="n">
         <v>788</v>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>22.84263959390863</v>
+        <v>44.1624365482</v>
       </c>
       <c r="I64" t="n">
         <v>788</v>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>25</v>
+        <v>47.3350253807</v>
       </c>
       <c r="I65" t="n">
         <v>788</v>
